--- a/fhir/StructureDefinition-ehealth-actionguidance.xlsx
+++ b/fhir/StructureDefinition-ehealth-actionguidance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -350,7 +350,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -684,7 +684,7 @@
     <t>Basic.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -731,7 +731,7 @@
     <t>Basic.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1058,7 +1058,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.3671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="83.5546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/fhir/StructureDefinition-ehealth-actionguidance.xlsx
+++ b/fhir/StructureDefinition-ehealth-actionguidance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-actionguidance.xlsx
+++ b/fhir/StructureDefinition-ehealth-actionguidance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-actionguidance.xlsx
+++ b/fhir/StructureDefinition-ehealth-actionguidance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-actionguidance.xlsx
+++ b/fhir/StructureDefinition-ehealth-actionguidance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-actionguidance.xlsx
+++ b/fhir/StructureDefinition-ehealth-actionguidance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-actionguidance.xlsx
+++ b/fhir/StructureDefinition-ehealth-actionguidance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
